--- a/materials/session_04/Bikesales.xlsx
+++ b/materials/session_04/Bikesales.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Lehre\Introduction to Programming\Exercises_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688AD6C4-3214-42BB-B0FA-AB1E1D33C489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23083" windowHeight="15480"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables1" sheetId="1" r:id="rId1"/>
@@ -19,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -67,7 +57,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -128,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -405,95 +395,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.15234375" customWidth="1"/>
-    <col min="4" max="4" width="11.15234375" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B3" s="2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="2">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>7797</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2">
+        <v>5</v>
+      </c>
       <c r="C3" s="2">
-        <v>3</v>
+        <v>18995</v>
       </c>
       <c r="D3" s="2">
-        <v>7797</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4410</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>5</v>
+        <v>5799</v>
       </c>
       <c r="D4" s="2">
-        <v>18995</v>
-      </c>
-      <c r="E4" s="2">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2">
+        <v>4</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>29996</v>
       </c>
       <c r="D5" s="2">
-        <v>5799</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>19200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>89910</v>
       </c>
       <c r="D6" s="2">
-        <v>29996</v>
-      </c>
-      <c r="E6" s="2">
-        <v>19200</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2">
-        <v>89910</v>
-      </c>
-      <c r="E7" s="2">
         <v>75600</v>
       </c>
     </row>
